--- a/Shopping_W_data.xlsx
+++ b/Shopping_W_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6aa8e1dd04d46e4d/Desktop/shopping_site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_F776CC53B6A7003596CC8056306D9B931B3C4078" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17578B1F-6157-4E82-9E74-01A11CAFE9FD}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_F776CC53B6A7003596CC8056306D9B931B3C4078" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9129CB27-FA56-4DAA-AC00-624511E626C2}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="176">
   <si>
     <t>userid</t>
   </si>
@@ -531,25 +531,25 @@
     <t>date</t>
   </si>
   <si>
-    <t>action</t>
-  </si>
-  <si>
     <t>product_id</t>
   </si>
   <si>
     <t>qty</t>
   </si>
   <si>
-    <t>UI003</t>
-  </si>
-  <si>
     <t>Yogi</t>
   </si>
   <si>
-    <t>ab.c@gmail.com</t>
-  </si>
-  <si>
     <t>a</t>
+  </si>
+  <si>
+    <t>.@gmail</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>m</t>
   </si>
 </sst>
 </file>
@@ -613,7 +613,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -624,6 +624,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3135,7 +3136,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="19.81640625" customWidth="1"/>
@@ -3171,30 +3172,30 @@
     </row>
     <row r="3" spans="1:4" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>171</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
+        <v>171</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>173</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="12.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>172</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>174</v>
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>175</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="12.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3205,11 +3206,10 @@
     <row r="10" spans="1:4" ht="12.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="11" spans="1:4" ht="12.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="1:4" ht="12.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:4" ht="12.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C4" r:id="rId1" xr:uid="{A8CCB46B-59F7-4D08-97E7-7AAC6D55EAC7}"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{A8CCB46B-59F7-4D08-97E7-7AAC6D55EAC7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3220,8 +3220,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
@@ -3237,7 +3240,24 @@
         <v>170</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="8">
+        <v>46218</v>
+      </c>
+      <c r="C2">
+        <v>11049</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/Shopping_W_data.xlsx
+++ b/Shopping_W_data.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -84,6 +84,9 @@
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -93,7 +96,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -101,12 +104,18 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,6 +133,9 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3134,7 +3146,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -3222,6 +3234,28 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>Yogi@1234</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>UI003</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>yogi</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>testing2@gmail.com</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1234@Yogi</t>
         </is>
       </c>
     </row>
@@ -3237,45 +3271,45 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>OrderID</t>
-        </is>
-      </c>
-      <c r="B1" s="9" t="inlineStr">
-        <is>
-          <t>UserID</t>
-        </is>
-      </c>
-      <c r="C1" s="12" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D1" s="9" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>orderid</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>userid</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>p_id</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="F1" s="9" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="12.5" customHeight="1">
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>UI001O1</t>
@@ -3296,10 +3330,8 @@
           <t>PIBS1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E2" t="n">
+        <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -3307,7 +3339,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="12.5" customHeight="1">
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>UI002O1</t>
@@ -3328,10 +3360,8 @@
           <t>PIBS1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E3" t="n">
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -3360,10 +3390,8 @@
           <t>PIBTS1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E4" t="n">
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -3392,10 +3420,8 @@
           <t>PIBS1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="E5" t="n">
+        <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -3424,10 +3450,8 @@
           <t>11038</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="E6" t="n">
+        <v>2</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -3435,7 +3459,37 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UI003O1</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>UI003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>20/07/26||29/07/26</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PIBW1</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Shopping_W_data.xlsx
+++ b/Shopping_W_data.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -79,9 +79,12 @@
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -96,12 +99,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -132,8 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -3237,7 +3257,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="12.5" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
           <t>UI003</t>
@@ -3274,7 +3294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3308,6 +3328,11 @@
           <t>size</t>
         </is>
       </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -3338,6 +3363,11 @@
           <t>M</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3352,7 +3382,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19/07/26||28/07/26</t>
+          <t>19/07/26||21/07/26</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3368,6 +3398,11 @@
           <t>M</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3398,6 +3433,11 @@
           <t>M</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3428,6 +3468,11 @@
           <t>M</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3442,7 +3487,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19/07/26||28/07/26</t>
+          <t>19/07/26||21/07/26</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3458,6 +3503,11 @@
           <t>M</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3486,6 +3536,83 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>M</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UI002O5</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>UI002</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>15/07/26||20/07/26</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PIBS1</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UI002O6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>UI002</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>21/07/26||30/07/26</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PIBGW</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ordered</t>
         </is>
       </c>
     </row>

--- a/Shopping_W_data.xlsx
+++ b/Shopping_W_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="product_data" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,19 +11,26 @@
     <sheet name="users_history" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <color rgb="FF000000"/>
       <sz val="10"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -43,8 +50,8 @@
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
@@ -56,36 +63,15 @@
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="2"/>
       <color theme="10"/>
       <sz val="10"/>
       <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="8"/>
-      <scheme val="minor"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -99,29 +85,8 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
+  <borders count="2">
+    <border/>
     <border>
       <left style="thin"/>
       <right style="thin"/>
@@ -131,29 +96,28 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -316,6 +280,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -342,24 +307,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -420,12 +386,11 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -435,875 +400,875 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:F80"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63281" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="12.6328125" customWidth="1" min="1" max="1"/>
-    <col width="37.36328125" customWidth="1" min="2" max="2"/>
-    <col width="12.6328125" customWidth="1" min="3" max="3"/>
-    <col width="53.08984375" customWidth="1" min="4" max="4"/>
-    <col width="15.36328125" customWidth="1" min="5" max="6"/>
+    <col width="12.63281" customWidth="1" min="1" max="1"/>
+    <col width="37.36328" customWidth="1" min="2" max="2"/>
+    <col width="12.63281" customWidth="1" min="3" max="3"/>
+    <col width="53.08984" customWidth="1" min="4" max="4"/>
+    <col width="15.36328" customWidth="1" min="5" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>P_ID</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>P_Name</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>P_Price</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>P_Description</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>P_Rating</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>PIBP1</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Men’s Casual Cotton Shirt</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Men’s Denim Jeans</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
         <v>799</v>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Soft cotton fabric, slim fit, suitable for daily wear.</t>
         </is>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>men jeans pant</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>PIBS1</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Men’s Formal Office Shirt</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1199</v>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Premium fabric with regular fit, ideal for office use.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>mens Shirt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>PIBS3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Black Slim Fit Suit</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>4599</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>A stylish slim-fit black blazer designed for a modern and elegant look. Perfect for formal events, office wear, parties, and special occasions.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>mens</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>PIBS1</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Men’s Formal Office Shirt</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>1199</v>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Premium fabric with regular fit, ideal for office use.</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>PIBS2</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Men’s Casual Cotton Shirt </t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1499</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Stretchable denim, comfortable for long wear.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>mens Shirt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>PIBSP1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Men’s Traditional Kurta</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1299</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Ethnic wear suitable for festivals and functions.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>mens</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>PIBS3</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Black Slim Fit Suit</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>4599</v>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>A stylish slim-fit black blazer designed for a modern and elegant look. Perfect for formal events, office wear, parties, and special occasions.</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>mens</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>PIBS2</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Men’s Denim Jeans</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>PIBTS1</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Full Sleeve ombre zip-up jecket</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1299</v>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Premium white-to-black gradient hoodie with soft cotton fabric, full zip closure, and comfortable fit for casual wear.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>mens jecket</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>PIBTS2</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Forest Shadow T-Shirt</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Stylish white t-shirt featuring a black forest silhouette print. Lightweight and breathable for daily use.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>mens T-Shirt</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>PIBTS3</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Dual Tone T-Shirt</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>749</v>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Modern black and white abstract design t-shirt made from high-quality cotton with a regular fit.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>mens T-Shirt</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>PIBTS4</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Split Graphic Hoodie</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>1499</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Stretchable denim, comfortable for long wear.</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>mens</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>PIBSP1</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Men’s Traditional Kurta</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>1299</v>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Ethnic wear suitable for festivals and functions.</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>mens</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>PIBTS1</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Full Sleeve ombre zip-up jecket</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>1299</v>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Premium white-to-black gradient hoodie with soft cotton fabric, full zip closure, and comfortable fit for casual wear.</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="n">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Trendy dual-color hoodie with graphic artwork, adjustable hood, and front pockets for extra comfort.</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>mens</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>PIBTS2</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Forest Shadow T-Shirt</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>699</v>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>Stylish white t-shirt featuring a black forest silhouette print. Lightweight and breathable for daily use.</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>mens</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>PIBTS3</t>
-        </is>
-      </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Abstract Dual Tone T-Shirt</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>749</v>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>Modern black and white abstract design t-shirt made from high-quality cotton with a regular fit.</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>mens</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>PIBTS4</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>Split Graphic Hoodie</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="n">
-        <v>1499</v>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>Trendy dual-color hoodie with graphic artwork, adjustable hood, and front pockets for extra comfort.</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>mens</t>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>mens Hoodie</t>
         </is>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>PIBTS5</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Vintage Streetwear Tee</t>
         </is>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>899</v>
       </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Casual oversized streetwear t-shirt with vintage-inspired print and relaxed fit for everyday fashion.</t>
         </is>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="2" t="n">
         <v>4.7</v>
       </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>mens</t>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>mens T-Shirt</t>
         </is>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1"/>
     <row r="13" ht="15.75" customHeight="1"/>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>11016</v>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Women’s Floral Kurti</t>
         </is>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>899</v>
       </c>
-      <c r="D14" s="1" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Elegant floral print with comfortable fit.</t>
         </is>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="F14" s="1" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>womens Kurti</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>11017</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Women’s Casual Top</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Trendy design, suitable for daily wear.</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>womens  Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>11018</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Women's Stylish Lime Green Casual Top</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>This is a solid green, regular-fit top crafted from Viscose Rayon fabric.</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>womens  Top</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>11019</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Women’s Party Wear Dress</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>1999</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Stylish party dress with premium finish.</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>womens Dress</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>11020</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Buggered - Mint Embellished Dhoti Jumpsuit.</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1399</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>This designer ensemble features a dhoti-style jumpsuit crafted from a blend of raw silk and Swiss cotton.</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>womens</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1" t="n">
-        <v>11017</v>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>Women’s Casual Top</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>699</v>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Trendy design, suitable for daily wear.</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>womens</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="1" t="n">
-        <v>11018</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Women's Stylish Lime Green Casual Top</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>899</v>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>This is a solid green, regular-fit top crafted from Viscose Rayon fabric.</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>womens</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="1" t="n">
-        <v>11019</v>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>Women’s Party Wear Dress</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>1999</v>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Stylish party dress with premium finish.</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>womens</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="1" t="n">
-        <v>11020</v>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>Buggered - Mint Embellished Dhoti Jumpsuit.</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="n">
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>11021</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Women’s Traditional Saree</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>2499</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Soft fabric saree with rich border design.</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>womens Saree</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>11022</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Women’s Denim Jeans</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>1399</v>
       </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>This designer ensemble features a dhoti-style jumpsuit crafted from a blend of raw silk and Swiss cotton.</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F18" s="1" t="inlineStr">
-        <is>
-          <t>womens</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="1" t="n">
-        <v>11021</v>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>Women’s Traditional Saree</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>2499</v>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Soft fabric saree with rich border design.</t>
-        </is>
-      </c>
-      <c r="E19" s="1" t="n">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Stretchable jeans with modern fit.</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>womens Jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>11023</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Women's Jeans</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1299</v>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Slim-fit stretchable denim jeans.</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>womens Jeans</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>11044</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Women's Saree</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2199</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Designer saree suitable for festive occasions.</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="F19" s="1" t="inlineStr">
-        <is>
-          <t>womens</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="1" t="n">
-        <v>11022</v>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>Women’s Denim Jeans</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>1399</v>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Stretchable jeans with modern fit.</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>womens</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="1" t="n">
-        <v>11023</v>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Women's Jeans</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="n">
-        <v>1299</v>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>Slim-fit stretchable denim jeans.</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>womens</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="1" t="n">
-        <v>11044</v>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Women's Saree</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="n">
-        <v>2199</v>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Designer saree suitable for festive occasions.</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>womens</t>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>womens Saree</t>
         </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>11024</v>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Redmi Note 13 Pro</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n">
+      <c r="C25" s="5" t="n">
         <v>18999</v>
       </c>
-      <c r="D25" s="1" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Smartphone A1 (6GB RAM, 128GB Storage), 6.67-inch AMOLED display, 108MP camera, long battery life.</t>
         </is>
       </c>
-      <c r="E25" s="1" t="n">
+      <c r="E25" s="2" t="n">
         <v>4.8</v>
       </c>
-      <c r="F25" s="1" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>11025</v>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Samsung Galaxy A14</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n">
+      <c r="C26" s="3" t="n">
         <v>13499</v>
       </c>
-      <c r="D26" s="1" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Flagship device with premium build quality. Budget smartphone with smooth performance and good battery backup.</t>
         </is>
       </c>
-      <c r="E26" s="1" t="n">
+      <c r="E26" s="2" t="n">
         <v>4.8</v>
       </c>
-      <c r="F26" s="1" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>11026</v>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Samsung Galaxy S20 FE</t>
         </is>
       </c>
-      <c r="C27" s="2" t="n">
+      <c r="C27" s="3" t="n">
         <v>24999</v>
       </c>
-      <c r="D27" s="1" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Smartphone B2 (8GB RAM, 128GB Storage). Premium design, powerful processor, excellent camera quality.</t>
         </is>
       </c>
-      <c r="E27" s="1" t="n">
+      <c r="E27" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="F27" s="1" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>11027</v>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>Vivo Y200 Pro</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n">
+      <c r="C28" s="3" t="n">
         <v>19999</v>
       </c>
-      <c r="D28" s="1" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Stylish smartphone with fast charging support. Affordable phone for daily usage.</t>
         </is>
       </c>
-      <c r="E28" s="1" t="n">
+      <c r="E28" s="2" t="n">
         <v>4.7</v>
       </c>
-      <c r="F28" s="1" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>11028</v>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>OnePlus Nord CE</t>
         </is>
       </c>
-      <c r="C29" s="2" t="n">
+      <c r="C29" s="3" t="n">
         <v>21999</v>
       </c>
-      <c r="D29" s="1" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fast 5G connectivity with advanced camera. Fast performance, clean UI, and AMOLED display.</t>
         </is>
       </c>
-      <c r="E29" s="1" t="n">
+      <c r="E29" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="F29" s="1" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>11029</v>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>Redmi 9 Power</t>
         </is>
       </c>
-      <c r="C30" s="2" t="n">
+      <c r="C30" s="3" t="n">
         <v>14999</v>
       </c>
-      <c r="D30" s="1" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Smartphone A1 (6GB RAM, 128GB Storage). Powerful processor with long-lasting battery. </t>
         </is>
       </c>
-      <c r="E30" s="1" t="n">
+      <c r="E30" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="F30" s="1" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>11030</v>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>Vivo Y200 Pro</t>
         </is>
       </c>
-      <c r="C31" s="2" t="n">
+      <c r="C31" s="3" t="n">
         <v>15999</v>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>Good gaming performance and attractive design.</t>
         </is>
       </c>
-      <c r="E31" s="1" t="n">
+      <c r="E31" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="F31" s="1" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>11031</v>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Motorola Moto G</t>
         </is>
       </c>
-      <c r="C32" s="2" t="n">
+      <c r="C32" s="3" t="n">
         <v>12999</v>
       </c>
-      <c r="D32" s="1" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Flagship device with premium build quality.</t>
         </is>
       </c>
-      <c r="E32" s="1" t="n">
+      <c r="E32" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="F32" s="1" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>11045</v>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Redmi A3X</t>
         </is>
       </c>
-      <c r="C33" s="2" t="n">
+      <c r="C33" s="3" t="n">
         <v>8999</v>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>Entry-level smartphone suitable for daily tasks.</t>
         </is>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="E33" s="4" t="n">
         <v>4.1</v>
       </c>
-      <c r="F33" s="1" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>11046</v>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Poco X6</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
+      <c r="C34" s="3" t="n">
         <v>22999</v>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>High refresh rate display and powerful chipset.</t>
         </is>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="E34" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="F34" s="1" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>11053</v>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Fast Charging Adapter</t>
         </is>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>999</v>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>33W charger with USB cable included.</t>
         </is>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="E35" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="F35" s="1" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>PIMPRE</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Realme 12 plus 5G</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
+      <c r="C36" s="3" t="n">
         <v>22999</v>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>Affordable smartphone with modern design.</t>
         </is>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="E36" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="F36" s="1" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>mobiles</t>
         </is>
@@ -1312,130 +1277,130 @@
     <row r="37" ht="15.75" customHeight="1"/>
     <row r="38" ht="15.75" customHeight="1"/>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>11032</v>
       </c>
-      <c r="B39" s="1" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>Men’s Comfort Slippers</t>
         </is>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>499</v>
       </c>
-      <c r="D39" s="1" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Lightweight and comfortable for daily use.</t>
         </is>
       </c>
-      <c r="E39" s="1" t="n">
+      <c r="E39" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="F39" s="1" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>men slippers</t>
         </is>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>11033</v>
       </c>
-      <c r="B40" s="1" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>Unisex Home Slippers</t>
         </is>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>598</v>
       </c>
-      <c r="D40" s="1" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Simple and durable home slippers.</t>
         </is>
       </c>
-      <c r="E40" s="1" t="n">
+      <c r="E40" s="2" t="n">
         <v>4.1</v>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>men slippers</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>11034</v>
       </c>
-      <c r="B41" s="1" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>Women’s Stylish Slippers</t>
         </is>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>599</v>
       </c>
-      <c r="D41" s="1" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Trendy design with soft sole.</t>
         </is>
       </c>
-      <c r="E41" s="1" t="n">
+      <c r="E41" s="2" t="n">
         <v>4.7</v>
       </c>
-      <c r="F41" s="1" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>women slippers</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>11035</v>
       </c>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>Unisex Home Slippers</t>
         </is>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>399</v>
       </c>
-      <c r="D42" s="1" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Simple and durable home slippers.</t>
         </is>
       </c>
-      <c r="E42" s="1" t="n">
+      <c r="E42" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="1" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>women slippers</t>
         </is>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>11036</v>
       </c>
-      <c r="B43" s="1" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Men’s Comfort Slippers</t>
         </is>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>400</v>
       </c>
-      <c r="D43" s="1" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Lightweight and comfortable for daily use.</t>
         </is>
       </c>
-      <c r="E43" s="1" t="n">
+      <c r="E43" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="F43" s="1" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>women slippers</t>
         </is>
@@ -1444,346 +1409,346 @@
     <row r="44" ht="15.75" customHeight="1"/>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>11037</v>
       </c>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Men’s Running Shoes</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n">
+      <c r="C46" s="3" t="n">
         <v>1999</v>
       </c>
-      <c r="D46" s="1" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Lightweight shoes with strong grip.</t>
         </is>
       </c>
-      <c r="E46" s="1" t="n">
+      <c r="E46" s="2" t="n">
         <v>4.4</v>
       </c>
-      <c r="F46" s="1" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>men shoes</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>11038</v>
       </c>
-      <c r="B47" s="1" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>Sports Shoes (Unisex)</t>
         </is>
       </c>
-      <c r="C47" s="2" t="n">
+      <c r="C47" s="3" t="n">
         <v>2199</v>
       </c>
-      <c r="D47" s="1" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Durable sports shoes for training and walking.</t>
         </is>
       </c>
-      <c r="E47" s="1" t="n">
+      <c r="E47" s="2" t="n">
         <v>4.2</v>
       </c>
-      <c r="F47" s="1" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>men shoes</t>
         </is>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>11039</v>
       </c>
-      <c r="B48" s="1" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Women’s Casual Shoes</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
+      <c r="C48" s="3" t="n">
         <v>1799</v>
       </c>
-      <c r="D48" s="1" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Stylish shoes for daily wear.</t>
         </is>
       </c>
-      <c r="E48" s="1" t="n">
+      <c r="E48" s="2" t="n">
         <v>4.3</v>
       </c>
-      <c r="F48" s="1" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>women shoes</t>
         </is>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>11040</v>
       </c>
-      <c r="B49" s="1" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Men’s Formal Shoes</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C49" s="3" t="n">
         <v>2499</v>
       </c>
-      <c r="D49" s="1" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Classic design suitable for office wear.</t>
         </is>
       </c>
-      <c r="E49" s="1" t="n">
+      <c r="E49" s="2" t="n">
         <v>4.9</v>
       </c>
-      <c r="F49" s="1" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>men shoes</t>
         </is>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>11041</v>
       </c>
-      <c r="B50" s="1" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Women’s Casual Shoes</t>
         </is>
       </c>
-      <c r="C50" s="2" t="n">
+      <c r="C50" s="3" t="n">
         <v>1999</v>
       </c>
-      <c r="D50" s="1" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Lightweight shoes with strong grip.</t>
         </is>
       </c>
-      <c r="E50" s="1" t="n">
+      <c r="E50" s="2" t="n">
         <v>4.7</v>
       </c>
-      <c r="F50" s="1" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>men shoes</t>
         </is>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>11042</v>
       </c>
-      <c r="B51" s="1" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Sports Shoes (Unisex)</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
+      <c r="C51" s="3" t="n">
         <v>2199</v>
       </c>
-      <c r="D51" s="1" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> Durable sports shoes for training and walking.</t>
         </is>
       </c>
-      <c r="E51" s="1" t="n">
+      <c r="E51" s="2" t="n">
         <v>4.6</v>
       </c>
-      <c r="F51" s="1" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>men shoes</t>
         </is>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>11043</v>
       </c>
-      <c r="B52" s="1" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>Men’s Running Shoes</t>
         </is>
       </c>
-      <c r="C52" s="2" t="n">
+      <c r="C52" s="3" t="n">
         <v>2200</v>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>Durable sports shoes for walking and jogging.</t>
         </is>
       </c>
-      <c r="E52" s="1" t="n">
+      <c r="E52" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="F52" s="1" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>men shoes</t>
         </is>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="1" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="3" t="n"/>
-      <c r="E53" s="1" t="n"/>
-      <c r="F53" s="1" t="n"/>
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>11047</v>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Women's White Slippers</t>
         </is>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>599</v>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>Comfortable everyday slippers with soft sole.</t>
         </is>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="E54" s="4" t="n">
         <v>4.3</v>
       </c>
-      <c r="F54" s="3" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>women Slippers</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>11048</v>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Pink Sandals</t>
         </is>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>699</v>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>Lightweight sandals with modern design.</t>
         </is>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="E55" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="F55" s="3" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>women Slippers</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>11049</v>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Sports Running Shoes</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
+      <c r="C56" s="3" t="n">
         <v>1899</v>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>Comfortable running shoes with cushioned sole</t>
         </is>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="E56" s="4" t="n">
         <v>4.4</v>
       </c>
-      <c r="F56" s="1" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>men shoes</t>
         </is>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>11050</v>
       </c>
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Men's Running Shoes</t>
         </is>
       </c>
-      <c r="C57" s="2" t="n">
+      <c r="C57" s="3" t="n">
         <v>2299</v>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="D57" s="4" t="inlineStr">
         <is>
           <t>Durable sports shoes for walking and jogging.</t>
         </is>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="E57" s="4" t="n">
         <v>4.2</v>
       </c>
-      <c r="F57" s="1" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>men shoes</t>
         </is>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>11051</v>
       </c>
-      <c r="B58" s="3" t="inlineStr">
+      <c r="B58" s="4" t="inlineStr">
         <is>
           <t>Women's Flats</t>
         </is>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>799</v>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="D58" s="4" t="inlineStr">
         <is>
           <t>Soft and stylish flats for daily wear.</t>
         </is>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="E58" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="F58" s="1" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>women shoes</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>11052</v>
       </c>
-      <c r="B59" s="3" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>Women's Sneakers</t>
         </is>
       </c>
-      <c r="C59" s="2" t="n">
+      <c r="C59" s="3" t="n">
         <v>1599</v>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>Trendy sneakers with excellent comfort.</t>
         </is>
       </c>
-      <c r="E59" s="3" t="n">
+      <c r="E59" s="4" t="n">
         <v>4.7</v>
       </c>
-      <c r="F59" s="1" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>women shoes</t>
         </is>
@@ -1791,444 +1756,419 @@
     </row>
     <row r="60" ht="15.75" customHeight="1"/>
     <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="3" t="n">
-        <v>1133</v>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Gaming Laptop</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>59999</v>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>High-performance laptop for gaming and productivity.</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="n">
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="4" t="n">
+        <v>4500</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Men's Formal Shoes</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1499</v>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>Premium leather-look formal shoes.</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>men shoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="4" t="n">
+        <v>4511</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Rose Gold Watch</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>2999</v>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>Elegant watch with premium metal strap.</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="n">
         <v>4.7</v>
       </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>laptop</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="3" t="n">
-        <v>4500</v>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Men's Formal Shoes</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>1499</v>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>Premium leather-look formal shoes.</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n">
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>men watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="4" t="n">
+        <v>4522</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Men's Casual Shirt</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>Cotton shirt perfect for casual outings.</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>mens Shirt</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="4" t="n">
+        <v>4533</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Women's Green Gown</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1799</v>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>Elegant party wear gown with premium fabric.</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="n">
         <v>4.5</v>
       </c>
-      <c r="F64" s="1" t="inlineStr">
-        <is>
-          <t>men shoes</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="3" t="n">
-        <v>4511</v>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Rose Gold Watch</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>2999</v>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>Elegant watch with premium metal strap.</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="n">
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>womens Gown</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="4" t="n">
+        <v>4544</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Luxury Wrist Watch</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>2499</v>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>Stylish analog watch suitable for all occasions.</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>women watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="4" t="n">
+        <v>4555</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Women's Casual Shoes</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>Comfortable lightweight slip-on shoes.</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>women shoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>PIGW1</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>Women's Cute Cat Face Watch</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>699</v>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>Cute cat-face dial with soft silicone strap. Lightweight and perfect for daily wear.</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>women watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>PIGW2</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Women's Marble Dial Watch</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>849</v>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Elegant marble-pattern dial with rose gold finish and comfortable silicone strap.</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>women watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>PIGW3</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Women's Geneva Classic Watch</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>999</v>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>Stylish Geneva analog watch featuring a premium white silicone strap.</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="n">
         <v>4.7</v>
       </c>
-      <c r="F65" s="5" t="inlineStr">
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>women watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>PIGW4</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>Women's Minimal Square Watch</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>899</v>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Modern square dial watch with soft silicone strap.</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>men and women watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>PIBGW</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>Unisex Classic Silicone Watch</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>799</v>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>Minimal analog watch with soft silicone strap suitable for men and women.</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <t>men watch</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3" t="n">
-        <v>4522</v>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Men's Casual Shirt</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="n">
-        <v>799</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>Cotton shirt perfect for casual outings.</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>mens</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="3" t="n">
-        <v>4533</v>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Women's Green Gown</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>1799</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>Elegant party wear gown with premium fabric.</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>womens</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="3" t="n">
-        <v>4544</v>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Luxury Wrist Watch</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="n">
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>PIBW1</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Men's Luxury Leather Watch</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="n">
         <v>2499</v>
       </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Stylish analog watch suitable for all occasions.</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n">
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Premium leather strap watch with elegant blue dial and calendar display.</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>men watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>PIBW2</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>Men's Premium Steel Watch</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>3199</v>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>Stainless steel analog watch with black dial and luxury finish.</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>men watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>PIBW3</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Men's Automatic Skeleton Watch</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="n">
+        <v>4299</v>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Mechanical automatic skeleton dial watch with premium metal strap.</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>men watch</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>PIBW4</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Men's Imperious Green Watch</t>
+        </is>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>2799</v>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>Modern green dial analog watch with black case.</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="n">
         <v>4.6</v>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>women watch</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="3" t="n">
-        <v>4555</v>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Women's Casual Shoes</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="n">
-        <v>899</v>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>Comfortable lightweight slip-on shoes.</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F70" s="1" t="inlineStr">
-        <is>
-          <t>women shoes</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>PIGW1</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>Women's Cute Cat Face Watch</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="n">
-        <v>699</v>
-      </c>
-      <c r="D73" s="5" t="inlineStr">
-        <is>
-          <t>Cute cat-face dial with soft silicone strap. Lightweight and perfect for daily wear.</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>women watch</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>PIGW2</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>Women's Marble Dial Watch</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="n">
-        <v>849</v>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>Elegant marble-pattern dial with rose gold finish and comfortable silicone strap.</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>women watch</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>PIGW3</t>
-        </is>
-      </c>
-      <c r="B75" s="5" t="inlineStr">
-        <is>
-          <t>Women's Geneva Classic Watch</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="n">
-        <v>999</v>
-      </c>
-      <c r="D75" s="5" t="inlineStr">
-        <is>
-          <t>Stylish Geneva analog watch featuring a premium white silicone strap.</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>women watch</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>PIGW4</t>
-        </is>
-      </c>
-      <c r="B76" s="5" t="inlineStr">
-        <is>
-          <t>Women's Minimal Square Watch</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="n">
-        <v>899</v>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>Modern square dial watch with soft silicone strap.</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>men and women watch</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
-        <is>
-          <t>PIBGW</t>
-        </is>
-      </c>
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>Unisex Classic Silicone Watch</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="n">
-        <v>799</v>
-      </c>
-      <c r="D77" s="5" t="inlineStr">
-        <is>
-          <t>Minimal analog watch with soft silicone strap suitable for men and women.</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="F77" s="5" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <t>men watch</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>PIBW1</t>
-        </is>
-      </c>
-      <c r="B78" s="5" t="inlineStr">
-        <is>
-          <t>Men's Luxury Leather Watch</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="n">
-        <v>2499</v>
-      </c>
-      <c r="D78" s="5" t="inlineStr">
-        <is>
-          <t>Premium leather strap watch with elegant blue dial and calendar display.</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>men watch</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>PIBW2</t>
-        </is>
-      </c>
-      <c r="B79" s="5" t="inlineStr">
-        <is>
-          <t>Men's Premium Steel Watch</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="n">
-        <v>3199</v>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>Stainless steel analog watch with black dial and luxury finish.</t>
-        </is>
-      </c>
-      <c r="E79" s="6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>men watch</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>PIBW3</t>
-        </is>
-      </c>
-      <c r="B80" s="5" t="inlineStr">
-        <is>
-          <t>Men's Automatic Skeleton Watch</t>
-        </is>
-      </c>
-      <c r="C80" s="6" t="n">
-        <v>4299</v>
-      </c>
-      <c r="D80" s="5" t="inlineStr">
-        <is>
-          <t>Mechanical automatic skeleton dial watch with premium metal strap.</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>men watch</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="5" t="inlineStr">
-        <is>
-          <t>PIBW4</t>
-        </is>
-      </c>
-      <c r="B81" s="5" t="inlineStr">
-        <is>
-          <t>Men's Imperious Green Watch</t>
-        </is>
-      </c>
-      <c r="C81" s="6" t="n">
-        <v>2799</v>
-      </c>
-      <c r="D81" s="5" t="inlineStr">
-        <is>
-          <t>Modern green dial analog watch with black case.</t>
-        </is>
-      </c>
-      <c r="E81" s="6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>men watch</t>
-        </is>
-      </c>
-    </row>
+    <row r="81" ht="15.75" customHeight="1"/>
     <row r="82" ht="15.75" customHeight="1"/>
     <row r="83" ht="15.75" customHeight="1"/>
     <row r="84" ht="15.75" customHeight="1"/>
@@ -3153,7 +3093,6 @@
     <row r="1003" ht="15.75" customHeight="1"/>
     <row r="1004" ht="15.75" customHeight="1"/>
     <row r="1005" ht="15.75" customHeight="1"/>
-    <row r="1006" ht="15.75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -3166,50 +3105,60 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6328125" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63281" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>UserID</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>UserName</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>password</t>
         </is>
       </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Yogi</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Yogi</t>
         </is>
       </c>
-      <c r="C2" s="11" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>.@gmail</t>
         </is>
       </c>
-      <c r="D2" s="8" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>a</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
     </row>
@@ -3234,6 +3183,11 @@
           <t>Yogi@123</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="12.5" customHeight="1">
       <c r="A4" t="inlineStr">
@@ -3256,6 +3210,11 @@
           <t>Yogi@1234</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="12.5" customHeight="1">
       <c r="A5" t="inlineStr">
@@ -3276,6 +3235,65 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>1234@Yogi</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>UI004</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>yogi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>testing3@gmail.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Yogi@123</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>UI005</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>siva</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>siva@gmail.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Siva@1234</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>User</t>
         </is>
       </c>
     </row>
@@ -3283,7 +3301,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait"/>
 </worksheet>
 </file>
@@ -3294,41 +3312,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>orderid</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>userid</t>
         </is>
       </c>
-      <c r="C1" s="13" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D1" s="13" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>p_id</t>
         </is>
       </c>
-      <c r="E1" s="13" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="F1" s="13" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>size</t>
         </is>
       </c>
-      <c r="G1" s="13" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -3365,7 +3383,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
@@ -3435,7 +3453,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3488,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3558,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
@@ -3600,10 +3618,8 @@
           <t>PIBGW</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="E9" t="n">
+        <v>3</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3612,7 +3628,147 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ordered</t>
+          <t>Delivered</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UI002O7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>UI002</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22/07/26||31/07/26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11033</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UI002O8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>UI002</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>22/07/26||25/07/26</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>11028</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>nosize</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>YogiO1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Yogi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>07/08/26||10/08/26</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>UI005O1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>UI005</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>21/08/26||24/08/26</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PIBS1</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>

--- a/Shopping_W_data.xlsx
+++ b/Shopping_W_data.xlsx
@@ -3312,7 +3312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3772,6 +3772,76 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>YogiO2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Yogi</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>08/09/26||11/09/26</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PIBTS1</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>10</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UI001O2</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>UI001</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>09/09/26||12/09/26</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PIBTS4</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>shipping</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Shopping_W_data.xlsx
+++ b/Shopping_W_data.xlsx
@@ -3105,7 +3105,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63281" defaultRowHeight="15" customHeight="1"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Yogi</t>
+          <t>BlackGoshter</t>
         </is>
       </c>
       <c r="C2" s="10" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>yogi</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Yogi@123</t>
+          <t>Testing@009</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yogi</t>
+          <t>Testing1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Yogi@1234</t>
+          <t>Testing@010</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yogi</t>
+          <t>Testing2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1234@Yogi</t>
+          <t>Testing@011</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yogi</t>
+          <t>Testing3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Yogi@123</t>
+          <t>Testing@012</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3292,6 +3292,60 @@
         </is>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>UI006</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>tester</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>testing4@gmail.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Testing@014</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UI007</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>testing5@gmail.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Testing@014</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>User</t>
         </is>
@@ -3803,7 +3857,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3892,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>shipping</t>
+          <t>Delivered</t>
         </is>
       </c>
     </row>
